--- a/analisis/wb_2026-10-07_resultados.xlsx
+++ b/analisis/wb_2026-10-07_resultados.xlsx
@@ -28,6 +28,30 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="C45" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">ROI 19 del fichero de cuantificación (3 610). Lo tenías medido pero sin asignar: es este fragmento.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">El gel 4 no tiene ROI para el fragmento. Estimado al 40 % de la banda principal, que es la proporción que da mi densitometría sobre la imagen en los DOS geles (0,40 y 0,39). Es una estimación, no una medida tuya.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E7" authorId="0">
       <text>
         <r>
@@ -69,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="180">
   <si>
     <t xml:space="preserve">Western blot 2026-10-07 — resultados</t>
   </si>
@@ -251,6 +275,36 @@
     <t xml:space="preserve">3610, gel 3, fondo 0,977 (el triple del resto). ¿Banda inferior, degradación, o mancha?</t>
   </si>
   <si>
+    <t xml:space="preserve">RESULTADO 3 — wt3 produce un fragmento de K10 sin extremo C-terminal, y mut1 no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banda inferior en el blot de anti-K10, sólo en wt3, en los dos geles (25–29x sobre fondo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La ve anti-K10 pero no anti-Myc-DDK → ha perdido el C-terminal, donde va el tag. Es K10 recortado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausente en mut1, en KerCT WT y en el KO, así que sigue al transgén de wt3 y a nada más.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es el ROI 19 (3 610) que estaba sin asignar en tu fichero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFECTA AL RESULTADO 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los valores de anti-K10 son K10 de longitud completa, no K10 total. Sumando el fragmento, la ventaja de mut1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desaparece (gel 4: 1,01x) o se invierte (gel 3: 0,77x). Ver hoja 'Geles 3-4 - K10', sección 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para 'el mutante falla pese a tener K10' la banda principal es la medida correcta y la conclusión aguanta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para 'cuánta proteína K10 hay' hay que sumar el fragmento. Declara cuál usas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Geles 3 y 4 — líneas estables de K10: wt3 vs mut1</t>
   </si>
   <si>
@@ -329,6 +383,51 @@
     <t xml:space="preserve">Los carriles mut1 van sistemáticamente más cargados. Por eso el cociente en bruto exagera la diferencia.</t>
   </si>
   <si>
+    <t xml:space="preserve">5. El fragmento de K10 — banda inferior del blot de anti-K10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visible en la Figura 1. Presente SÓLO en wt3 y en los dos geles; ausente en mut1, en KerCT WT y en el KO de K10. Lo detecta anti-K10 pero NO anti-Myc-DDK,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">así que ha perdido el extremo C-terminal, que es donde va el tag. Es K10 recortado, no una proteína distinta: sigue al transgén de wt3 y a nada más.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wt3 banda principal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wt3 fragmento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wt3 TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wt3 total normaliz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mut1 normaliz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mut1 / wt3 con fragmento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gel 4 (estimado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consecuencia: los valores de anti-K10 de la sección 3 son K10 DE LONGITUD COMPLETA, no K10 total. Contando el fragmento, la ventaja de mut1 desaparece</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(gel 4) o se invierte (gel 3). Cuál de los dos números quieres depende de la pregunta: para '¿tiene el mutante K10 funcional suficiente?' la banda principal es</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la medida correcta y la conclusión aguanta; para '¿cuánta proteína K10 hay?' hay que sumar el fragmento. Dilo explícitamente: el doblete se ve en la figura y te lo van a preguntar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esto explica además por qué los dos anticuerpos no concuerdan (1,32x con anti-K10 frente a 1,79x con anti-Myc-DDK): si parte del fragmento cae dentro de la caja de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la banda principal de wt3, infla la lectura de anti-K10 en wt3 y reduce el cociente. anti-Myc-DDK no tiene ese problema, pero está saturado. Ninguno de los dos es limpio.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gel 2 — anti-K1 (canal 785), 7 muestras</t>
   </si>
   <si>
@@ -417,6 +516,9 @@
   </si>
   <si>
     <t xml:space="preserve">explicaría el descenso por sí solo. Un carril de KerCT + plásmido vacío lo resuelve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Figura</t>
   </si>
   <si>
     <t xml:space="preserve">Trazabilidad — los 39 ROIs de Image Studio</t>
@@ -722,12 +824,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -735,7 +841,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -747,11 +853,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -759,7 +865,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -767,15 +873,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -783,47 +889,51 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -831,43 +941,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1012,6 +1118,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="1"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1094,6 +1201,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="1"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1154,17 +1262,17 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-15"/>
-        <c:axId val="14311672"/>
-        <c:axId val="6062576"/>
+        <c:axId val="65246503"/>
+        <c:axId val="50487589"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14311672"/>
+        <c:axId val="65246503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1190,7 +1298,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6062576"/>
+        <c:crossAx val="50487589"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1198,7 +1306,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="6062576"/>
+        <c:axId val="50487589"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1238,7 +1346,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1264,7 +1372,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14311672"/>
+        <c:crossAx val="65246503"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1385,6 +1493,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="1"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1467,6 +1576,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="1"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1527,17 +1637,17 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="-15"/>
-        <c:axId val="61846827"/>
-        <c:axId val="2804523"/>
+        <c:axId val="70874984"/>
+        <c:axId val="68489568"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61846827"/>
+        <c:axId val="70874984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1563,7 +1673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2804523"/>
+        <c:crossAx val="68489568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1571,7 +1681,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2804523"/>
+        <c:axId val="68489568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1611,7 +1721,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1637,7 +1747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61846827"/>
+        <c:crossAx val="70874984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1758,6 +1868,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:numFmt formatCode="0.000" sourceLinked="1"/>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
@@ -1848,17 +1959,17 @@
         </c:ser>
         <c:gapWidth val="45"/>
         <c:overlap val="0"/>
-        <c:axId val="28222138"/>
-        <c:axId val="88632172"/>
+        <c:axId val="89414133"/>
+        <c:axId val="19831646"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28222138"/>
+        <c:axId val="89414133"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1884,7 +1995,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88632172"/>
+        <c:crossAx val="19831646"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1892,7 +2003,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88632172"/>
+        <c:axId val="19831646"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1932,7 +2043,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1958,7 +2069,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28222138"/>
+        <c:crossAx val="89414133"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1997,9 +2108,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>399240</xdr:colOff>
+      <xdr:colOff>398520</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>21960</xdr:rowOff>
+      <xdr:rowOff>21240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2007,8 +2118,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8364960" y="762120"/>
-        <a:ext cx="4679640" cy="3059640"/>
+        <a:off x="8364960" y="761040"/>
+        <a:ext cx="4678920" cy="3051000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2027,9 +2138,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>399240</xdr:colOff>
+      <xdr:colOff>398520</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>61920</xdr:rowOff>
+      <xdr:rowOff>61200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2037,8 +2148,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8364960" y="4381560"/>
-        <a:ext cx="4679640" cy="3059640"/>
+        <a:off x="8364960" y="4372560"/>
+        <a:ext cx="4678920" cy="3051360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2046,6 +2157,43 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>69120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>102240</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>58680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10784880"/>
+          <a:ext cx="11524680" cy="8561880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2062,18 +2210,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>364680</xdr:colOff>
+      <xdr:colOff>363960</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>41040</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="3" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7871400" y="762120"/>
-        <a:ext cx="6479640" cy="3419640"/>
+        <a:off x="7871400" y="761040"/>
+        <a:ext cx="6478920" cy="3403440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2081,6 +2229,43 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>595800</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>180360</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 2" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5838840"/>
+          <a:ext cx="11524680" cy="3799800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2266,327 +2451,380 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="104"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="104"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2605,530 +2843,661 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="10" t="n">
+      <c r="B6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <v>13400</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <v>1030</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="13" t="n">
         <f aca="false">E6/G6</f>
         <v>13.0097087378641</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="14" t="n">
+      <c r="B7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>41900</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="17" t="n">
         <v>1370</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <f aca="false">E7/G7</f>
         <v>30.5839416058394</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="10" t="n">
+      <c r="B8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <v>19200</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <v>1120</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="13" t="n">
         <f aca="false">E8/G8</f>
         <v>17.1428571428571</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="14" t="n">
+      <c r="B9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>40100</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>1910</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">E9/G9</f>
         <v>20.9947643979058</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="10" t="n">
+      <c r="B10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <v>3790</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="13" t="n">
         <f aca="false">E10/G10</f>
         <v>2.98425196850394</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="14" t="n">
+      <c r="B11" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>6860</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>1620</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">E11/G11</f>
         <v>4.23456790123457</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="10" t="n">
+      <c r="B12" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <v>6130</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <v>1710</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="13" t="n">
         <f aca="false">E12/G12</f>
         <v>3.58479532163743</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="14" t="n">
+      <c r="B13" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>8230</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>1880</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <f aca="false">E13/G13</f>
         <v>4.37765957446809</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <f aca="false">H6</f>
         <v>13.0097087378641</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <f aca="false">H7</f>
         <v>30.5839416058394</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="19" t="n">
         <f aca="false">C18/B18</f>
         <v>2.35085521298616</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <f aca="false">H8</f>
         <v>17.1428571428571</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="13" t="n">
         <f aca="false">H9</f>
         <v>20.9947643979058</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="19" t="n">
         <f aca="false">C19/B19</f>
         <v>1.22469458987784</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="20" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="21" t="n">
         <f aca="false">AVERAGE(B18:B19)</f>
         <v>15.0762829403606</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="21" t="n">
         <f aca="false">AVERAGE(C18:C19)</f>
         <v>25.7893530018726</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
         <f aca="false">AVERAGE(D18:D19)</f>
         <v>1.787774901432</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <f aca="false">H10</f>
         <v>2.98425196850394</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="13" t="n">
         <f aca="false">H11</f>
         <v>4.23456790123457</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <f aca="false">C26/B26</f>
         <v>1.41897130199681</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <f aca="false">H12</f>
         <v>3.58479532163743</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="13" t="n">
         <f aca="false">H13</f>
         <v>4.37765957446809</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="19" t="n">
         <f aca="false">C27/B27</f>
         <v>1.22117420429697</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="20" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="21" t="n">
         <f aca="false">AVERAGE(B26:B27)</f>
         <v>3.28452364507068</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="21" t="n">
         <f aca="false">AVERAGE(C26:C27)</f>
         <v>4.30611373785133</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="22" t="n">
         <f aca="false">AVERAGE(D26:D27)</f>
         <v>1.32007275314689</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="11" t="n">
+      <c r="C34" s="12" t="n">
         <f aca="false">G6</f>
         <v>1030</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <f aca="false">G7</f>
         <v>1370</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="19" t="n">
         <f aca="false">D34/C34</f>
         <v>1.33009708737864</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="11" t="n">
+      <c r="B35" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="12" t="n">
         <f aca="false">G8</f>
         <v>1120</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="12" t="n">
         <f aca="false">G9</f>
         <v>1910</v>
       </c>
-      <c r="E35" s="18" t="n">
+      <c r="E35" s="19" t="n">
         <f aca="false">D35/C35</f>
         <v>1.70535714285714</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="11" t="n">
+      <c r="B36" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="12" t="n">
         <f aca="false">G10</f>
         <v>1270</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="12" t="n">
         <f aca="false">G11</f>
         <v>1620</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="19" t="n">
         <f aca="false">D36/C36</f>
         <v>1.2755905511811</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="11" t="n">
+      <c r="B37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="12" t="n">
         <f aca="false">G12</f>
         <v>1710</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="12" t="n">
         <f aca="false">G13</f>
         <v>1880</v>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="19" t="n">
         <f aca="false">D37/C37</f>
         <v>1.09941520467836</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>85</v>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="12" t="n">
+        <f aca="false">E12</f>
+        <v>6130</v>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>3610</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <f aca="false">B45+C45</f>
+        <v>9740</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <f aca="false">G12</f>
+        <v>1710</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <f aca="false">D45/E45</f>
+        <v>5.69590643274854</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <f aca="false">H13</f>
+        <v>4.37765957446809</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <f aca="false">G45/F45</f>
+        <v>0.768562409891214</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="12" t="n">
+        <f aca="false">E10</f>
+        <v>3790</v>
+      </c>
+      <c r="C46" s="23" t="n">
+        <f aca="false">B46*0.4</f>
+        <v>1516</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <f aca="false">B46+C46</f>
+        <v>5306</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <f aca="false">G10</f>
+        <v>1270</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <f aca="false">D46/E46</f>
+        <v>4.17795275590551</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <f aca="false">H11</f>
+        <v>4.23456790123457</v>
+      </c>
+      <c r="H46" s="19" t="n">
+        <f aca="false">G46/F46</f>
+        <v>1.01355092999772</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3149,347 +3518,352 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="10" t="n">
+      <c r="B6" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <v>8500</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>2820</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">D6/F6</f>
         <v>3.01418439716312</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="27" t="n">
         <f aca="false">G6/$G$6</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="26" t="n">
+      <c r="B7" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="28" t="n">
         <v>34</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="23" t="n">
         <v>1400</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="31" t="n">
         <f aca="false">D7/F7</f>
         <v>0.0114285714285714</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="32" t="n">
         <f aca="false">G7/$G$6</f>
         <v>0.00379159663865546</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="30" t="n">
         <v>99.8</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="23" t="n">
         <v>2090</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <f aca="false">D8/F8</f>
         <v>0.0477511961722488</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="32" t="n">
         <f aca="false">G8/$G$6</f>
         <v>0.0158421615536167</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="10" t="n">
+      <c r="B9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <v>2000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>2160</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">D9/F9</f>
         <v>0.925925925925926</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="27" t="n">
         <f aca="false">G9/$G$6</f>
         <v>0.30718954248366</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="10" t="n">
+      <c r="B10" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="25" t="n">
         <v>1060</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>1270</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="26" t="n">
         <f aca="false">D10/F10</f>
         <v>0.834645669291339</v>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="27" t="n">
         <f aca="false">G10/$G$6</f>
         <v>0.276905974988421</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="B11" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="25" t="n">
         <v>661</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>1450</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">D11/F11</f>
         <v>0.455862068965517</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="27" t="n">
         <f aca="false">G11/$G$6</f>
         <v>0.151238945233266</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="B12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="25" t="n">
         <v>754</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>2390</v>
       </c>
-      <c r="G12" s="24" t="n">
+      <c r="G12" s="26" t="n">
         <f aca="false">D12/F12</f>
         <v>0.315481171548117</v>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="27" t="n">
         <f aca="false">G12/$G$6</f>
         <v>0.104665518090081</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="24" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">G7</f>
         <v>0.0114285714285714</v>
       </c>
-      <c r="C18" s="24" t="n">
+      <c r="C18" s="26" t="n">
         <f aca="false">G10</f>
         <v>0.834645669291339</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="33" t="n">
         <f aca="false">C18/B18</f>
         <v>73.0314960629921</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="24" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="26" t="n">
         <f aca="false">G8</f>
         <v>0.0477511961722488</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="26" t="n">
         <f aca="false">G11</f>
         <v>0.455862068965517</v>
       </c>
-      <c r="D19" s="32" t="n">
+      <c r="D19" s="33" t="n">
         <f aca="false">C19/B19</f>
         <v>9.54661046230392</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>115</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3513,1247 +3887,1247 @@
   <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="8" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <v>41900</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <v>44400</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>5704</v>
+      </c>
+      <c r="I5" s="35" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>260</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <v>6596</v>
+      </c>
+      <c r="I6" s="35" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>13400</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <v>15400</v>
+      </c>
+      <c r="H7" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <v>2050</v>
+      </c>
+      <c r="H8" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I8" s="35" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>1370</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <v>2320</v>
+      </c>
+      <c r="H9" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>2100</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I10" s="35" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>2990</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I11" s="35" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>19200</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>21300</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>5060</v>
+      </c>
+      <c r="I12" s="35" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>40100</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>42900</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <v>5400</v>
+      </c>
+      <c r="I13" s="35" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>3790</v>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>5140</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I14" s="35" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <v>6860</v>
+      </c>
+      <c r="G15" s="34" t="n">
+        <v>8020</v>
+      </c>
+      <c r="H15" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I15" s="35" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>2730</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I16" s="35" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>2250</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I17" s="35" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>1880</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>2760</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I18" s="35" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="34" t="n">
+        <v>1710</v>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>2610</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I19" s="35" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="34" t="n">
+        <v>6130</v>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>4558</v>
+      </c>
+      <c r="I20" s="35" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>8230</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>10600</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>4558</v>
+      </c>
+      <c r="I21" s="35" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>3610</v>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>8070</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>4558</v>
+      </c>
+      <c r="I22" s="35" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>-0.0284</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>203</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>4558</v>
+      </c>
+      <c r="I23" s="35" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="F24" s="34" t="n">
+        <v>92.4</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I24" s="35" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="36" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G25" s="36" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H25" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I25" s="37" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="J25" s="14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="F26" s="34" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>1840</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I26" s="35" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G27" s="36" t="n">
+        <v>616</v>
+      </c>
+      <c r="H27" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="F28" s="34" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>1880</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I28" s="35" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="36" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G29" s="36" t="n">
+        <v>706</v>
+      </c>
+      <c r="H29" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I29" s="37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="F30" s="34" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I30" s="35" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G31" s="36" t="n">
+        <v>2640</v>
+      </c>
+      <c r="H31" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I31" s="37" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="F32" s="34" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>2060</v>
+      </c>
+      <c r="H32" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I32" s="35" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F33" s="36" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G33" s="36" t="n">
+        <v>1730</v>
+      </c>
+      <c r="H33" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I33" s="37" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="36" t="n">
+        <v>754</v>
+      </c>
+      <c r="G34" s="36" t="n">
+        <v>1280</v>
+      </c>
+      <c r="H34" s="36" t="n">
+        <v>3403</v>
+      </c>
+      <c r="I34" s="37" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="33" t="n">
-        <v>41900</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>44400</v>
-      </c>
-      <c r="H5" s="33" t="n">
-        <v>5704</v>
-      </c>
-      <c r="I5" s="34" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="F35" s="36" t="n">
+        <v>661</v>
+      </c>
+      <c r="G35" s="36" t="n">
+        <v>1350</v>
+      </c>
+      <c r="H35" s="36" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I35" s="37" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="34" t="n">
+        <v>2820</v>
+      </c>
+      <c r="G36" s="34" t="n">
+        <v>4540</v>
+      </c>
+      <c r="H36" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G37" s="34" t="n">
+        <v>3100</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>5046</v>
+      </c>
+      <c r="I37" s="35" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="34" t="n">
+        <v>2090</v>
+      </c>
+      <c r="G38" s="34" t="n">
+        <v>3350</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>3871</v>
+      </c>
+      <c r="I38" s="35" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G39" s="34" t="n">
+        <v>3400</v>
+      </c>
+      <c r="H39" s="34" t="n">
+        <v>3871</v>
+      </c>
+      <c r="I39" s="35" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="34" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G40" s="34" t="n">
+        <v>2550</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>3871</v>
+      </c>
+      <c r="I40" s="35" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G41" s="34" t="n">
+        <v>2760</v>
+      </c>
+      <c r="H41" s="34" t="n">
+        <v>3871</v>
+      </c>
+      <c r="I41" s="35" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E42" s="10" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="G6" s="33" t="n">
-        <v>260</v>
-      </c>
-      <c r="H6" s="33" t="n">
-        <v>6596</v>
-      </c>
-      <c r="I6" s="34" t="n">
-        <v>0.0399</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>13400</v>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>15400</v>
-      </c>
-      <c r="H7" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I7" s="34" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>1030</v>
-      </c>
-      <c r="G8" s="33" t="n">
-        <v>2050</v>
-      </c>
-      <c r="H8" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I8" s="34" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>1370</v>
-      </c>
-      <c r="G9" s="33" t="n">
-        <v>2320</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I9" s="34" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G10" s="33" t="n">
-        <v>2100</v>
-      </c>
-      <c r="H10" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I10" s="34" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>1910</v>
-      </c>
-      <c r="G11" s="33" t="n">
-        <v>2990</v>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I11" s="34" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>19200</v>
-      </c>
-      <c r="G12" s="33" t="n">
-        <v>21300</v>
-      </c>
-      <c r="H12" s="33" t="n">
-        <v>5060</v>
-      </c>
-      <c r="I12" s="34" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>40100</v>
-      </c>
-      <c r="G13" s="33" t="n">
-        <v>42900</v>
-      </c>
-      <c r="H13" s="33" t="n">
-        <v>5400</v>
-      </c>
-      <c r="I13" s="34" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="33" t="n">
-        <v>3790</v>
-      </c>
-      <c r="G14" s="33" t="n">
-        <v>5140</v>
-      </c>
-      <c r="H14" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I14" s="34" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="33" t="n">
-        <v>6860</v>
-      </c>
-      <c r="G15" s="33" t="n">
-        <v>8020</v>
-      </c>
-      <c r="H15" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I15" s="34" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="33" t="n">
-        <v>1620</v>
-      </c>
-      <c r="G16" s="33" t="n">
-        <v>2730</v>
-      </c>
-      <c r="H16" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I16" s="34" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="33" t="n">
-        <v>1270</v>
-      </c>
-      <c r="G17" s="33" t="n">
-        <v>2250</v>
-      </c>
-      <c r="H17" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I17" s="34" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="33" t="n">
-        <v>1880</v>
-      </c>
-      <c r="G18" s="33" t="n">
-        <v>2760</v>
-      </c>
-      <c r="H18" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I18" s="34" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="33" t="n">
-        <v>1710</v>
-      </c>
-      <c r="G19" s="33" t="n">
-        <v>2610</v>
-      </c>
-      <c r="H19" s="33" t="n">
-        <v>2886</v>
-      </c>
-      <c r="I19" s="34" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="33" t="n">
-        <v>6130</v>
-      </c>
-      <c r="G20" s="33" t="n">
-        <v>8400</v>
-      </c>
-      <c r="H20" s="33" t="n">
-        <v>4558</v>
-      </c>
-      <c r="I20" s="34" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="33" t="n">
-        <v>8230</v>
-      </c>
-      <c r="G21" s="33" t="n">
-        <v>10600</v>
-      </c>
-      <c r="H21" s="33" t="n">
-        <v>4558</v>
-      </c>
-      <c r="I21" s="34" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="33" t="n">
-        <v>3610</v>
-      </c>
-      <c r="G22" s="33" t="n">
-        <v>8070</v>
-      </c>
-      <c r="H22" s="33" t="n">
-        <v>4558</v>
-      </c>
-      <c r="I22" s="34" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="33" t="n">
-        <v>-0.0284</v>
-      </c>
-      <c r="G23" s="33" t="n">
-        <v>203</v>
-      </c>
-      <c r="H23" s="33" t="n">
-        <v>4558</v>
-      </c>
-      <c r="I23" s="34" t="n">
-        <v>0.0445</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F24" s="33" t="n">
-        <v>92.4</v>
-      </c>
-      <c r="G24" s="33" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H24" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I24" s="34" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>8500</v>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>9200</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I25" s="36" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="33" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="G26" s="33" t="n">
-        <v>1840</v>
-      </c>
-      <c r="H26" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I26" s="34" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>16</v>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>616</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I27" s="36" t="n">
-        <v>0.119</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="33" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="G28" s="33" t="n">
-        <v>1880</v>
-      </c>
-      <c r="H28" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I28" s="34" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>706</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I29" s="36" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="G30" s="33" t="n">
-        <v>1920</v>
-      </c>
-      <c r="H30" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I30" s="34" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" s="35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G31" s="35" t="n">
-        <v>2640</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I31" s="36" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="33" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="G32" s="33" t="n">
-        <v>2060</v>
-      </c>
-      <c r="H32" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I32" s="34" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="J32" s="9"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33" s="35" t="n">
-        <v>1060</v>
-      </c>
-      <c r="G33" s="35" t="n">
-        <v>1730</v>
-      </c>
-      <c r="H33" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I33" s="36" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="35" t="n">
-        <v>754</v>
-      </c>
-      <c r="G34" s="35" t="n">
-        <v>1280</v>
-      </c>
-      <c r="H34" s="35" t="n">
-        <v>3403</v>
-      </c>
-      <c r="I34" s="36" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F35" s="35" t="n">
-        <v>661</v>
-      </c>
-      <c r="G35" s="35" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H35" s="35" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I35" s="36" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="33" t="n">
-        <v>2820</v>
-      </c>
-      <c r="G36" s="33" t="n">
-        <v>4540</v>
-      </c>
-      <c r="H36" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I36" s="34" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="33" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G37" s="33" t="n">
-        <v>3100</v>
-      </c>
-      <c r="H37" s="33" t="n">
-        <v>5046</v>
-      </c>
-      <c r="I37" s="34" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F38" s="33" t="n">
-        <v>2090</v>
-      </c>
-      <c r="G38" s="33" t="n">
-        <v>3350</v>
-      </c>
-      <c r="H38" s="33" t="n">
+      <c r="F42" s="34" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G42" s="34" t="n">
+        <v>3870</v>
+      </c>
+      <c r="H42" s="34" t="n">
         <v>3871</v>
       </c>
-      <c r="I38" s="34" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="F39" s="33" t="n">
-        <v>2160</v>
-      </c>
-      <c r="G39" s="33" t="n">
-        <v>3400</v>
-      </c>
-      <c r="H39" s="33" t="n">
-        <v>3871</v>
-      </c>
-      <c r="I39" s="34" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F40" s="33" t="n">
-        <v>1270</v>
-      </c>
-      <c r="G40" s="33" t="n">
-        <v>2550</v>
-      </c>
-      <c r="H40" s="33" t="n">
-        <v>3871</v>
-      </c>
-      <c r="I40" s="34" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F41" s="33" t="n">
-        <v>1450</v>
-      </c>
-      <c r="G41" s="33" t="n">
-        <v>2760</v>
-      </c>
-      <c r="H41" s="33" t="n">
-        <v>3871</v>
-      </c>
-      <c r="I41" s="34" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="33" t="n">
-        <v>2390</v>
-      </c>
-      <c r="G42" s="33" t="n">
-        <v>3870</v>
-      </c>
-      <c r="H42" s="33" t="n">
-        <v>3871</v>
-      </c>
-      <c r="I42" s="34" t="n">
+      <c r="I42" s="35" t="n">
         <v>0.384</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
-        <v>153</v>
+      <c r="J42" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
